--- a/output/details/2026-05-28/preprocessed_data.xlsx
+++ b/output/details/2026-05-28/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46170</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1167882234995906</v>
+        <v>-0.1228273917666461</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1375713519554364</v>
+        <v>-0.1426103580834757</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1373871988866511</v>
+        <v>-0.1423320276704931</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1187229926753044</v>
+        <v>-0.004238066695992698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001696730809124253</v>
+        <v>0.001692060248354683</v>
       </c>
       <c r="G2" t="n">
-        <v>1.981667914601885</v>
+        <v>2.536557142206702</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4328157050846197</v>
+        <v>-0.2679240277243761</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
